--- a/Analysed/Gemini/Combined_Analysis_Summary_flash_naive.xlsx
+++ b/Analysed/Gemini/Combined_Analysis_Summary_flash_naive.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.8104 ± 2.2271</t>
+          <t>4.5423 ± 4.4959</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.2551 ± 2.3866</t>
+          <t>5.3511 ± 5.2910</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6136 ± 0.2862</t>
+          <t>0.5964 ± 0.2930</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,20 +819,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V1_5 divisions_per_second</t>
+          <t>V2_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="D14" t="n">
-        <v>7.213333333333335</v>
+        <v>15.01930769230769</v>
       </c>
       <c r="E14" t="n">
-        <v>7.619672083932922</v>
+        <v>16.0257960080711</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9324324324324325</v>
+        <v>0.2248062015503876</v>
       </c>
     </row>
     <row r="15">
@@ -843,19 +843,115 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V2_10 divisions_per_second</t>
+          <t>V3_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>82</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14.49756097560976</v>
+      </c>
+      <c r="E15" t="n">
+        <v>18.44998717694049</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9012345679012346</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V4_1.7 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>55</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.208727272727274</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.702375650112433</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2407407407407407</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V5_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>46</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.689999999999998</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12.56977361354023</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V6_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7.213333333333335</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7.619672083932922</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9324324324324325</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V7_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>51</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D19" t="n">
         <v>5.663725490196079</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E19" t="n">
         <v>6.782044489015123</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F19" t="n">
         <v>0.8</v>
       </c>
     </row>
